--- a/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="355">
   <si>
     <t>Result</t>
   </si>
@@ -642,6 +642,468 @@
   </si>
   <si>
     <t>Sat Nov 08 13:56:05 IST 2025</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:27:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:31:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:33:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:37:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:37:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:38:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:40:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:42:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:43:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:45:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:46:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:46:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:48:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:49:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 01:50:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 23 01:57:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 23 19:49:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 21:41:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 21:44:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:00:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:04:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:06:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:09:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:11:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:25:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:31:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:32:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:37:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:39:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:41:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 22:57:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:01:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:05:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:09:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:19:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:21:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:22:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:25:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:27:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:29:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:32:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:33:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:34:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:36:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:37:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:38:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:40:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:41:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:42:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:47:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:49:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:51:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:54:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:56:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 29 23:59:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:02:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:03:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:04:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:06:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:07:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:08:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:10:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:11:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:18:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:21:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:24:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:49:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:52:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:54:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 00:57:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 01:35:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 01:38:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 01:40:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 01:49:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 01:51:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 01:53:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 01:57:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:00:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:02:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:05:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:06:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:08:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:10:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:11:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:12:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:14:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:14:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 02:16:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:43:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:45:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:47:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:51:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:53:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:55:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:58:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:59:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 13:00:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 13:03:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 13:04:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 13:04:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 13:06:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 13:07:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 13:08:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:17:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:20:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:22:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:26:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:29:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:31:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:35:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:36:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:37:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:39:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:43:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:43:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:45:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:46:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 14:47:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 20:19:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 19:54:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 19:59:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 20:04:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 20:10:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 20:15:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 20:33:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 20:37:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 20:41:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 20:45:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 21:02:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 21:08:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 21:12:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 21:50:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 21:56:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:03:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:12:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:20:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:25:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:28:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:38:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:41:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:44:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:46:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:48:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 22:50:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 02 23:50:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 03 01:01:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 03 01:18:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 03 19:57:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 03 20:08:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 03 20:12:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 03 20:14:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 03 20:23:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 03 20:31:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 03 20:33:22 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1494,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>341</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1129,10 +1591,10 @@
     </row>
     <row ht="29" r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>334</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1228,10 +1690,10 @@
     </row>
     <row ht="29" r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>333</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1324,10 +1786,10 @@
     </row>
     <row ht="29" r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>325</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1420,10 +1882,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>323</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1512,10 +1974,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>321</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1604,10 +2066,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>324</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1699,7 +2161,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>344</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1793,7 +2255,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>352</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1887,7 +2349,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>354</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1981,7 +2443,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>351</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2072,10 +2534,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>353</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2169,7 +2631,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>337</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2263,7 +2725,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>338</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2354,10 +2816,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>335</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2386" uniqueCount="485">
   <si>
     <t>Result</t>
   </si>
@@ -1104,6 +1104,396 @@
   </si>
   <si>
     <t>Tue Feb 03 20:33:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 03 21:20:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 22:50:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 22:51:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 22:53:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 22:57:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 22:59:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:01:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:04:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:05:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:06:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:08:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:09:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:10:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:12:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:13:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:14:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:49:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:51:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:53:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:57:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 05 23:59:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 06 00:01:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 06 00:04:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 06 00:05:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 06 00:06:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 06 00:08:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 06 00:09:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 06 00:10:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 06 00:12:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 06 00:13:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 06 00:14:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 09 22:07:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:04:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:06:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:09:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:15:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:17:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:20:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:24:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:25:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:26:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:29:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:30:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:31:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:34:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:34:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 01:36:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 19:47:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 19:50:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 10 19:52:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:21:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:23:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:26:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:30:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:33:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:35:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:40:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:44:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:48:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:51:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:53:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:57:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 02:59:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 03:01:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:36:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:37:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:40:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:43:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:46:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:48:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:51:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:52:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:53:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:55:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:56:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:57:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 06:59:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 07:00:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 07:01:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 18:43:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 18:46:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 18:50:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 18:54:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 19:04:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 19:17:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 20:21:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 20:25:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:03:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:05:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:06:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:10:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:11:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:13:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:16:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:17:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:19:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:21:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:22:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:23:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:24:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:25:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 08:26:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:19:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:20:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:23:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:27:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:30:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:33:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:36:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:37:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:41:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:43:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:44:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:45:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:47:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:48:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 14:49:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 20:43:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 20:55:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 21:04:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 21:07:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 22:10:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 22:28:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 22:32:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 22:39:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 23:35:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 18:19:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 19:05:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 19:46:16 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1884,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>341</v>
+        <v>468</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1594,7 +1984,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>334</v>
+        <v>484</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1693,7 +2083,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>333</v>
+        <v>483</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1789,7 +2179,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>325</v>
+        <v>482</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1885,7 +2275,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>323</v>
+        <v>481</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1977,7 +2367,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>321</v>
+        <v>476</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2069,7 +2459,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>480</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2161,7 +2551,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>344</v>
+        <v>469</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2255,7 +2645,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2349,7 +2739,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>354</v>
+        <v>471</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2443,7 +2833,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>351</v>
+        <v>472</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2534,10 +2924,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>353</v>
+        <v>470</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2628,10 +3018,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>337</v>
+        <v>465</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2725,7 +3115,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>338</v>
+        <v>466</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2816,10 +3206,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>464</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="183">
   <si>
     <t>Result</t>
   </si>
@@ -274,6 +274,354 @@
   </si>
   <si>
     <t>Wed Apr 08 19:53:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:50:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 17:54:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 17:55:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 17:56:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 17:57:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:06:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:57:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:58:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:59:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:03:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:05:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:07:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:11:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:12:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:13:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:15:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:16:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:17:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:19:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:20:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 22:21:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 23:42:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 23:43:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 23:46:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 23:50:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 23:52:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 23:54:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 23:57:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 23:58:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 23:59:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:02:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:03:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:03:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:05:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:06:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:07:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:11:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:12:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:14:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:15:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:19:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:20:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:21:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:23:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:24:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:27:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:29:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:32:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:35:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:43:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:48:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:49:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:49:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:51:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:55:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:59:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 01:07:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 01:11:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 01:12:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 01:14:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 01:15:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 01:16:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:17:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:19:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:20:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:22:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:24:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:26:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:30:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:31:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:32:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:34:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:35:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:36:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:38:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:39:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:40:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:44:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:45:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:46:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:48:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:51:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:53:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:54:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:56:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:57:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:00:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:02:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:05:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:08:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:11:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:16:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:21:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:22:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:22:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:24:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:28:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:32:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:40:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:44:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:45:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:47:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:48:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:49:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 18:03:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 18:18:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 18:26:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 18:33:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 18:43:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 18:50:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:02:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:05:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:08:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:18:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:33:33 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -664,7 +1012,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -758,7 +1106,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -850,7 +1198,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -942,7 +1290,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1034,7 +1382,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1126,7 +1474,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1218,7 +1566,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1310,7 +1658,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1404,7 +1752,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1495,10 +1843,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1589,10 +1937,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1686,7 +2034,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1780,7 +2128,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1871,10 +2219,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1965,10 +2313,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2062,7 +2410,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2152,6 +2500,12 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>135</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>13</v>
@@ -2244,7 +2598,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2338,7 +2692,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>182</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2428,6 +2782,12 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>180</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>13</v>
@@ -2520,10 +2880,10 @@
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2619,10 +2979,10 @@
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2718,7 +3078,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>166</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3208,7 +3568,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3304,7 +3664,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3400,7 +3760,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3496,7 +3856,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>164</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3688,7 +4048,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3780,7 +4140,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>171</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3874,7 +4234,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>173</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3966,7 +4326,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>156</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4058,7 +4418,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4150,7 +4510,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4242,7 +4602,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4331,10 +4691,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4426,7 +4786,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>174</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4518,7 +4878,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>175</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4610,7 +4970,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4702,7 +5062,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4888,7 +5248,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4982,7 +5342,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5076,10 +5436,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5173,7 +5533,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="243">
   <si>
     <t>Result</t>
   </si>
@@ -622,6 +622,186 @@
   </si>
   <si>
     <t>Tue May 05 19:33:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:35:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:36:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:37:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:41:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:44:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:46:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:50:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:51:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:52:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:54:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:55:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:56:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:58:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 00:58:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:00:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:04:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:05:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:06:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:07:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:11:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:12:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:13:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:15:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:16:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:19:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:21:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:24:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:27:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:32:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:40:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:41:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:41:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:43:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:47:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:51:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:58:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 02:02:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 02:03:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 02:05:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 02:06:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 02:07:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:06:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:12:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:17:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:19:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:28:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:30:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:32:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:36:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:40:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:43:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:48:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:53:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 20:59:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 21:06:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 21:09:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 21:12:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 21:13:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 21:16:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:39:20 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1192,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1106,7 +1286,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>202</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1198,7 +1378,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1290,7 +1470,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1382,7 +1562,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1474,7 +1654,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1566,7 +1746,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>242</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1658,7 +1838,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1752,7 +1932,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1843,10 +2023,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1937,10 +2117,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>221</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2034,7 +2214,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2128,7 +2308,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2219,10 +2399,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2316,7 +2496,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>227</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2410,7 +2590,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2504,7 +2684,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2598,7 +2778,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>239</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2692,7 +2872,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>240</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2783,10 +2963,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2880,10 +3060,10 @@
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2979,10 +3159,10 @@
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3078,7 +3258,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>219</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3568,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3664,7 +3844,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3760,7 +3940,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3856,7 +4036,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>241</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4048,7 +4228,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4140,7 +4320,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4234,7 +4414,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4326,7 +4506,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4418,7 +4598,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4510,7 +4690,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4602,7 +4782,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4694,7 +4874,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4786,7 +4966,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4878,7 +5058,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4970,7 +5150,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5062,7 +5242,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5248,7 +5428,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>220</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5342,7 +5522,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5436,10 +5616,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5530,10 +5710,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
